--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484102_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484102_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0062</v>
+        <v>2.7103</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1395</v>
+        <v>2.7313</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1332</v>
+        <v>-0.021</v>
       </c>
       <c r="G2" t="n">
         <v>2.8974</v>
@@ -610,13 +610,13 @@
         <v>0.7935</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3072</v>
+        <v>0.0113</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3685</v>
+        <v>-0.0396</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0612</v>
+        <v>0.051</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0466</v>
+        <v>0.3067</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4403</v>
+        <v>-0.2362</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4869</v>
+        <v>0.543</v>
       </c>
       <c r="G3" t="n">
         <v>-0.2006</v>
@@ -688,13 +688,13 @@
         <v>0.5952</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.348</v>
+        <v>-0.0878</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5611</v>
+        <v>-0.357</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2131</v>
+        <v>0.2692</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1793</v>
+        <v>-0.0429</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0046</v>
+        <v>0.1689</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1838</v>
+        <v>-0.2119</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1606</v>
@@ -766,13 +766,13 @@
         <v>0.9919</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0106</v>
+        <v>-0.8743</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.4591</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3872</v>
+        <v>-0.4152</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. NDIAYE</t>
+          <t>V. CEBRIA PUCHADES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.3931</v>
+        <v>-1.3841</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3685</v>
+        <v>0.0284</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7616</v>
+        <v>-1.4126</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4779</v>
+        <v>-0.6382</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4238</v>
+        <v>-1.1694</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9016999999999999</v>
+        <v>0.5312</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1778</v>
+        <v>1.3438</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0172</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1606</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.6557</v>
+        <v>-1.982</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.5934</v>
+        <v>-1.8655</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0623</v>
+        <v>-0.1165</v>
       </c>
       <c r="P5" t="n">
+        <v>0.7935</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-0.9919</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-2.9758</v>
-      </c>
       <c r="R5" t="n">
-        <v>1.9838</v>
+        <v>1.7855</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1893</v>
+        <v>-1.0075</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.306</v>
+        <v>-0.5894</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1167</v>
+        <v>-0.4181</v>
       </c>
       <c r="V5" t="n">
+        <v>-0.532</v>
+      </c>
+      <c r="W5" t="n">
         <v>0.266</v>
       </c>
-      <c r="W5" t="n">
-        <v>1.4724</v>
-      </c>
       <c r="X5" t="n">
-        <v>-1.2065</v>
+        <v>-0.7979000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. CEBRIA PUCHADES</t>
+          <t>L. NDIAYE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.8827</v>
+        <v>-1.643</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.442</v>
+        <v>0.0625</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4406</v>
+        <v>-1.7055</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6382</v>
+        <v>-0.4779</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1694</v>
+        <v>0.4238</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5312</v>
+        <v>-0.9016999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3438</v>
+        <v>2.1778</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6961000000000001</v>
+        <v>2.0172</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.1606</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.982</v>
+        <v>-2.6557</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.8655</v>
+        <v>-1.5934</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1165</v>
+        <v>-1.0623</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7935</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7855</v>
+        <v>1.9838</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.506</v>
+        <v>-0.4393</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0599</v>
+        <v>-0.6121</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4462</v>
+        <v>0.1728</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.532</v>
+        <v>0.266</v>
       </c>
       <c r="W6" t="n">
-        <v>0.266</v>
+        <v>1.4724</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2077</v>
+        <v>-2.1797</v>
       </c>
       <c r="E7" t="n">
         <v>0.6284999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.8362</v>
+        <v>-2.8082</v>
       </c>
       <c r="G7" t="n">
         <v>-0.352</v>
@@ -1000,13 +1000,13 @@
         <v>1.7855</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5538</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="T7" t="n">
         <v>-0.7481</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1944</v>
+        <v>0.2224</v>
       </c>
       <c r="V7" t="n">
         <v>-3.0874</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.484</v>
+        <v>-3.8028</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.6901</v>
+        <v>-4.5881</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2061</v>
+        <v>0.7853</v>
       </c>
       <c r="G8" t="n">
         <v>-1.8033</v>
@@ -1078,13 +1078,13 @@
         <v>1.3887</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.411</v>
+        <v>-0.7298</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8728</v>
+        <v>-0.7708</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4618</v>
+        <v>0.041</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6745</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7469</v>
+        <v>-3.9064</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3193</v>
+        <v>-2.563</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4276</v>
+        <v>-1.3434</v>
       </c>
       <c r="G9" t="n">
         <v>-0.6171</v>
@@ -1156,13 +1156,13 @@
         <v>0.9919</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.42</v>
+        <v>-0.5795</v>
       </c>
       <c r="T9" t="n">
-        <v>0.06809999999999999</v>
+        <v>-0.1757</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.488</v>
+        <v>-0.4039</v>
       </c>
       <c r="V9" t="n">
         <v>0.266</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9378</v>
+        <v>-4.1738</v>
       </c>
       <c r="E10" t="n">
-        <v>0.444</v>
+        <v>0.4043</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.3818</v>
+        <v>-4.5782</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6566</v>
@@ -1234,13 +1234,13 @@
         <v>1.1903</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3407</v>
+        <v>-0.5767</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3683</v>
+        <v>-0.408</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0277</v>
+        <v>-0.1687</v>
       </c>
       <c r="V10" t="n">
         <v>-2.1469</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9816</v>
+        <v>-4.5749</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7676</v>
+        <v>-2.5012</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.214</v>
+        <v>-2.0738</v>
       </c>
       <c r="G11" t="n">
         <v>-4.7351</v>
@@ -1312,13 +1312,13 @@
         <v>2.1822</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4368</v>
+        <v>-1.0301</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9862</v>
+        <v>-0.7198</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4506</v>
+        <v>-0.3104</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.335</v>
+        <v>-7.0927</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4968</v>
+        <v>-3.3947</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.8383</v>
+        <v>-3.698</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0658</v>
@@ -1390,13 +1390,13 @@
         <v>2.1822</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8563</v>
+        <v>-1.614</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1732</v>
+        <v>-1.0712</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6831</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-3.6194</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-26.0953</v>
+        <v>-25.7833</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.571000000000002</v>
+        <v>-9.2593</v>
       </c>
       <c r="F13" t="n">
-        <v>-16.5241</v>
+        <v>-16.5243</v>
       </c>
       <c r="G13" t="n">
         <v>-7.8098</v>
@@ -1468,13 +1468,13 @@
         <v>15.8707</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.7653</v>
+        <v>-7.453399999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.262500000000001</v>
+        <v>-5.9508</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.5026</v>
+        <v>-1.5027</v>
       </c>
       <c r="V13" t="n">
         <v>-9.5282</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.593</v>
+        <v>7.5837</v>
       </c>
       <c r="E14" t="n">
-        <v>3.974</v>
+        <v>4.5862</v>
       </c>
       <c r="F14" t="n">
-        <v>3.619</v>
+        <v>2.9975</v>
       </c>
       <c r="G14" t="n">
         <v>2.1156</v>
@@ -1546,13 +1546,13 @@
         <v>2.579</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9888</v>
+        <v>1.9795</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2777</v>
+        <v>0.3345</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2665</v>
+        <v>1.645</v>
       </c>
       <c r="V14" t="n">
         <v>3.8854</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. MAÑES CARRETERO</t>
+          <t>P. MULIO CAMPOS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.0168</v>
+        <v>6.05</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8404</v>
+        <v>1.6762</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1764</v>
+        <v>4.3738</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4154</v>
+        <v>3.112</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4281</v>
+        <v>3.1949</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8435</v>
+        <v>-0.0829</v>
       </c>
       <c r="J15" t="n">
-        <v>2.3205</v>
+        <v>2.4649</v>
       </c>
       <c r="K15" t="n">
-        <v>0.626</v>
+        <v>3.1049</v>
       </c>
       <c r="L15" t="n">
-        <v>1.6944</v>
+        <v>-0.64</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9051</v>
+        <v>0.6472</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0541</v>
+        <v>0.09</v>
       </c>
       <c r="O15" t="n">
-        <v>0.149</v>
+        <v>0.5572</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5952</v>
+        <v>0.1984</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R15" t="n">
-        <v>2.579</v>
+        <v>2.1822</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5933</v>
+        <v>0.8587</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8843</v>
+        <v>-0.0113</v>
       </c>
       <c r="U15" t="n">
-        <v>0.709</v>
+        <v>0.87</v>
       </c>
       <c r="V15" t="n">
-        <v>2.4129</v>
+        <v>1.881</v>
       </c>
       <c r="W15" t="n">
-        <v>3.6194</v>
+        <v>1.2065</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2065</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. MULIO CAMPOS</t>
+          <t>M. MAÑES CARRETERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.5416</v>
+        <v>5.5245</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4721</v>
+        <v>4.4322</v>
       </c>
       <c r="F16" t="n">
-        <v>4.0695</v>
+        <v>1.0923</v>
       </c>
       <c r="G16" t="n">
-        <v>3.112</v>
+        <v>1.4154</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1949</v>
+        <v>-0.4281</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0829</v>
+        <v>1.8435</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4649</v>
+        <v>2.3205</v>
       </c>
       <c r="K16" t="n">
-        <v>3.1049</v>
+        <v>0.626</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.64</v>
+        <v>1.6944</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6472</v>
+        <v>-0.9051</v>
       </c>
       <c r="N16" t="n">
-        <v>0.09</v>
+        <v>-1.0541</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5572</v>
+        <v>0.149</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1984</v>
+        <v>0.5952</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1822</v>
+        <v>2.579</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3503</v>
+        <v>1.101</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2153</v>
+        <v>0.4762</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5656</v>
+        <v>0.6248</v>
       </c>
       <c r="V16" t="n">
-        <v>1.881</v>
+        <v>2.4129</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2065</v>
+        <v>3.6194</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6745</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.8448</v>
+        <v>3.4928</v>
       </c>
       <c r="E17" t="n">
-        <v>4.5218</v>
+        <v>4.1137</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.677</v>
+        <v>-0.6209</v>
       </c>
       <c r="G17" t="n">
         <v>1.1305</v>
@@ -1780,13 +1780,13 @@
         <v>1.1903</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7063</v>
+        <v>0.3542</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3175</v>
+        <v>-0.0906</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3888</v>
+        <v>0.4449</v>
       </c>
       <c r="V17" t="n">
         <v>1.8097</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.402</v>
+        <v>3.441</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9408</v>
+        <v>2.4509</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4612</v>
+        <v>0.99</v>
       </c>
       <c r="G18" t="n">
         <v>1.8591</v>
@@ -1858,13 +1858,13 @@
         <v>1.9838</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5203</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3004</v>
+        <v>0.2098</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.22</v>
+        <v>0.3089</v>
       </c>
       <c r="V18" t="n">
         <v>0.0713</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.1817</v>
+        <v>2.2072</v>
       </c>
       <c r="E19" t="n">
-        <v>0.576</v>
+        <v>0.8821</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6057</v>
+        <v>1.3252</v>
       </c>
       <c r="G19" t="n">
         <v>1.2814</v>
@@ -1936,13 +1936,13 @@
         <v>0.5952</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0826</v>
+        <v>1.1081</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0227</v>
+        <v>0.3288</v>
       </c>
       <c r="U19" t="n">
-        <v>1.0599</v>
+        <v>0.7793</v>
       </c>
       <c r="V19" t="n">
         <v>1.2065</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. TUGORES SOTO</t>
+          <t>. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,75 +1969,71 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.8147</v>
+        <v>0.9198</v>
       </c>
       <c r="E20" t="n">
-        <v>2.252</v>
+        <v>0.037</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4373</v>
+        <v>0.8828</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1553</v>
+        <v>-0.9847</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4537</v>
+        <v>-0.0157</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.609</v>
+        <v>-0.969</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0988</v>
+        <v>0.3827</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9784</v>
+        <v>0.3024</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1205</v>
+        <v>0.0803</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.2541</v>
+        <v>-1.3674</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5246</v>
+        <v>-0.3181</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7295</v>
+        <v>-1.0493</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5952</v>
+        <v>1.5871</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>1.5871</v>
       </c>
       <c r="S20" t="n">
-        <v>2.3036</v>
+        <v>0.3174</v>
       </c>
       <c r="T20" t="n">
-        <v>1.5418</v>
+        <v>-0.3457</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7617</v>
+        <v>0.6631</v>
       </c>
       <c r="V20" t="n">
-        <v>0.0713</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>,. VICENTE SABARIEGO</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -2047,71 +2043,75 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5087</v>
+        <v>0.9198</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5051</v>
+        <v>0.037</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0036</v>
+        <v>0.8828</v>
       </c>
       <c r="G21" t="n">
-        <v>2.2687</v>
+        <v>-0.9847</v>
       </c>
       <c r="H21" t="n">
-        <v>2.2687</v>
+        <v>-0.0157</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-0.969</v>
       </c>
       <c r="J21" t="n">
-        <v>2.2687</v>
+        <v>0.3827</v>
       </c>
       <c r="K21" t="n">
-        <v>2.2687</v>
+        <v>0.3024</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.0803</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>-1.3674</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-0.3181</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-1.0493</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.9758</v>
+        <v>1.5871</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.5871</v>
       </c>
       <c r="S21" t="n">
-        <v>1.553</v>
+        <v>0.3174</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6802</v>
+        <v>-0.3457</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8728</v>
+        <v>0.6631</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3373</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>D. TUGORES SOTO</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -2121,73 +2121,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0186</v>
+        <v>0.7383</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.167</v>
+        <v>1.2317</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1856</v>
+        <v>-0.4934</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9847</v>
+        <v>-1.1553</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0157</v>
+        <v>0.4537</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.969</v>
+        <v>-1.609</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3827</v>
+        <v>1.0988</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3024</v>
+        <v>0.9784</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0803</v>
+        <v>0.1205</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3674</v>
+        <v>-2.2541</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3181</v>
+        <v>-0.5246</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0493</v>
+        <v>-1.7295</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5871</v>
+        <v>0.5952</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R22" t="n">
         <v>1.5871</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5838</v>
+        <v>1.2272</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5498</v>
+        <v>0.5215</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.034</v>
+        <v>0.7056</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.0713</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>. VICENTE SABARIEGO</t>
+          <t>P. SAIZ FUENTES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2199,58 +2199,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0186</v>
+        <v>0.5301</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.167</v>
+        <v>-1.3784</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1856</v>
+        <v>1.9086</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9847</v>
+        <v>-1.159</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0157</v>
+        <v>-0.6148</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.969</v>
+        <v>-0.5442</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3827</v>
+        <v>-1.5769</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3024</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0803</v>
+        <v>-0.6802</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3674</v>
+        <v>0.4179</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3181</v>
+        <v>0.2818</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0493</v>
+        <v>0.136</v>
       </c>
       <c r="P23" t="n">
-        <v>1.5871</v>
+        <v>1.1903</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5871</v>
+        <v>1.1903</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5838</v>
+        <v>0.4988</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5498</v>
+        <v>0.1984</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.034</v>
+        <v>0.3004</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2265,7 +2265,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. SAIZ FUENTES</t>
+          <t>,. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2277,67 +2277,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2045</v>
+        <v>-0.2735</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.8886</v>
+        <v>0.097</v>
       </c>
       <c r="F24" t="n">
-        <v>1.6841</v>
+        <v>-0.3704</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.159</v>
+        <v>2.2687</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6148</v>
+        <v>2.2687</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5442</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.5769</v>
+        <v>2.2687</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.8967000000000001</v>
+        <v>2.2687</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6802</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4179</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2818</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0.136</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1903</v>
+        <v>-2.9758</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1903</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2358</v>
+        <v>0.7708</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3117</v>
+        <v>0.2721</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0759</v>
+        <v>0.4988</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="25">
@@ -2355,13 +2355,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.6223</v>
+        <v>-3.1496</v>
       </c>
       <c r="E25" t="n">
         <v>-1.5023</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.1199</v>
+        <v>-1.6472</v>
       </c>
       <c r="G25" t="n">
         <v>-2.0739</v>
@@ -2400,13 +2400,13 @@
         <v>1.3887</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4727</v>
+        <v>-0</v>
       </c>
       <c r="T25" t="n">
         <v>-0.289</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1837</v>
+        <v>0.289</v>
       </c>
       <c r="V25" t="n">
         <v>-1.4724</v>
@@ -2433,16 +2433,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>26.1137</v>
+        <v>27.9841</v>
       </c>
       <c r="E26" t="n">
-        <v>16.3573</v>
+        <v>16.6633</v>
       </c>
       <c r="F26" t="n">
-        <v>9.756500000000001</v>
+        <v>11.3211</v>
       </c>
       <c r="G26" t="n">
-        <v>6.825099999999999</v>
+        <v>6.825100000000001</v>
       </c>
       <c r="H26" t="n">
         <v>10.4175</v>
@@ -2478,13 +2478,13 @@
         <v>18.4498</v>
       </c>
       <c r="S26" t="n">
-        <v>7.181500000000001</v>
+        <v>9.051699999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>0.9528000000000005</v>
+        <v>1.259</v>
       </c>
       <c r="U26" t="n">
-        <v>6.2285</v>
+        <v>7.7929</v>
       </c>
       <c r="V26" t="n">
         <v>9.5284</v>
@@ -2493,7 +2493,7 @@
         <v>14.3352</v>
       </c>
       <c r="X26" t="n">
-        <v>-4.8068</v>
+        <v>-4.806799999999999</v>
       </c>
     </row>
   </sheetData>
